--- a/online_avg_order_value.xlsx
+++ b/online_avg_order_value.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://yearuptemp-my.sharepoint.com/personal/tarista_my_yearupunited_org/Documents/Documents/DATA_Labs/Capstone_1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="64" documentId="8_{91A13794-A176-408E-AF20-8CCDBBAE1F9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6BE0425A-B28B-4688-8037-6D36FCCFF6AF}"/>
+  <xr:revisionPtr revIDLastSave="73" documentId="8_{91A13794-A176-408E-AF20-8CCDBBAE1F9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{40BB160B-6C50-4FDC-846F-B9A28CE402C7}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{E083B490-D4EB-4DBF-9EDA-D04AE57E27F1}"/>
+    <workbookView minimized="1" xWindow="2436" yWindow="3816" windowWidth="2388" windowHeight="564" activeTab="1" xr2:uid="{E083B490-D4EB-4DBF-9EDA-D04AE57E27F1}"/>
   </bookViews>
   <sheets>
     <sheet name="online_avg_order_value" sheetId="1" r:id="rId1"/>
@@ -525,10 +525,9 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -608,12 +607,9 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="tx2"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -622,19 +618,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>Average</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="en-US" baseline="0"/>
-              <a:t> order value in </a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="en-US"/>
-              <a:t>Online</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="en-US" baseline="0"/>
-              <a:t> sales</a:t>
+              <a:t>Average order value in Online sales</a:t>
             </a:r>
           </a:p>
           <a:p>
@@ -642,10 +626,9 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" baseline="0"/>
+              <a:rPr lang="en-US"/>
               <a:t>  in the East region </a:t>
             </a:r>
-            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:rich>
       </c:tx>
@@ -662,12 +645,9 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
+                <a:schemeClr val="tx2"/>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
@@ -700,9 +680,32 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent1">
+                    <a:satMod val="103000"/>
+                    <a:lumMod val="102000"/>
+                    <a:tint val="94000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="50000">
+                  <a:schemeClr val="accent1">
+                    <a:satMod val="110000"/>
+                    <a:lumMod val="100000"/>
+                    <a:shade val="100000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="99000"/>
+                    <a:satMod val="120000"/>
+                    <a:shade val="78000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -726,10 +729,7 @@
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
+                      <a:schemeClr val="tx2"/>
                     </a:solidFill>
                     <a:latin typeface="+mn-lt"/>
                     <a:ea typeface="+mn-ea"/>
@@ -752,14 +752,13 @@
                 <c15:showLeaderLines val="1"/>
                 <c15:leaderLines>
                   <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                    <a:ln w="9525">
                       <a:solidFill>
-                        <a:schemeClr val="tx1">
+                        <a:schemeClr val="tx2">
                           <a:lumMod val="35000"/>
                           <a:lumOff val="65000"/>
                         </a:schemeClr>
                       </a:solidFill>
-                      <a:round/>
                     </a:ln>
                     <a:effectLst/>
                   </c:spPr>
@@ -811,9 +810,32 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent2"/>
-            </a:solidFill>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent2">
+                    <a:satMod val="103000"/>
+                    <a:lumMod val="102000"/>
+                    <a:tint val="94000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="50000">
+                  <a:schemeClr val="accent2">
+                    <a:satMod val="110000"/>
+                    <a:lumMod val="100000"/>
+                    <a:shade val="100000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="99000"/>
+                    <a:satMod val="120000"/>
+                    <a:shade val="78000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -837,10 +859,7 @@
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
+                      <a:schemeClr val="tx2"/>
                     </a:solidFill>
                     <a:latin typeface="+mn-lt"/>
                     <a:ea typeface="+mn-ea"/>
@@ -863,14 +882,13 @@
                 <c15:showLeaderLines val="1"/>
                 <c15:leaderLines>
                   <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                    <a:ln w="9525">
                       <a:solidFill>
-                        <a:schemeClr val="tx1">
+                        <a:schemeClr val="tx2">
                           <a:lumMod val="35000"/>
                           <a:lumOff val="65000"/>
                         </a:schemeClr>
                       </a:solidFill>
-                      <a:round/>
                     </a:ln>
                     <a:effectLst/>
                   </c:spPr>
@@ -915,7 +933,8 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:gapWidth val="182"/>
+        <c:gapWidth val="100"/>
+        <c:overlap val="-24"/>
         <c:axId val="1185841279"/>
         <c:axId val="1185849439"/>
       </c:barChart>
@@ -934,7 +953,7 @@
           <a:noFill/>
           <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
-              <a:schemeClr val="tx1">
+              <a:schemeClr val="tx2">
                 <a:lumMod val="15000"/>
                 <a:lumOff val="85000"/>
               </a:schemeClr>
@@ -950,10 +969,7 @@
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="tx2"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -982,7 +998,7 @@
           <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
-                <a:schemeClr val="tx1">
+                <a:schemeClr val="tx2">
                   <a:lumMod val="15000"/>
                   <a:lumOff val="85000"/>
                 </a:schemeClr>
@@ -992,6 +1008,55 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx2"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t> value $</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx2"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="&quot;$&quot;#,##0.00" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -1004,16 +1069,13 @@
           <a:effectLst/>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="tx2"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -1052,10 +1114,7 @@
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
+                <a:schemeClr val="tx2"/>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
@@ -1083,7 +1142,7 @@
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
-        <a:schemeClr val="tx1">
+        <a:schemeClr val="tx2">
           <a:lumMod val="15000"/>
           <a:lumOff val="85000"/>
         </a:schemeClr>
@@ -1151,33 +1210,27 @@
 </file>
 
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="207">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
   </cs:axisTitle>
   <cs:categoryAxis>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
+          <a:schemeClr val="tx2">
             <a:lumMod val="15000"/>
             <a:lumOff val="85000"/>
           </a:schemeClr>
@@ -1192,7 +1245,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
@@ -1200,7 +1253,7 @@
       </a:solidFill>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
+          <a:schemeClr val="tx2">
             <a:lumMod val="15000"/>
             <a:lumOff val="85000"/>
           </a:schemeClr>
@@ -1208,17 +1261,14 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:dataLabel>
@@ -1227,9 +1277,8 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="dk2">
+        <a:lumMod val="75000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
@@ -1252,35 +1301,35 @@
   </cs:dataLabelCallout>
   <cs:dataPoint>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="3">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="3">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="28575" cap="rnd">
+      <a:ln w="31750" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -1289,33 +1338,32 @@
     </cs:spPr>
   </cs:dataPointLine>
   <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
+      <a:ln w="12700">
         <a:solidFill>
-          <a:schemeClr val="phClr"/>
+          <a:schemeClr val="lt2"/>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
   <cs:dataPointWireframe>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="rnd">
@@ -1331,21 +1379,16 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
+          <a:schemeClr val="tx2">
             <a:lumMod val="15000"/>
             <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
@@ -1355,23 +1398,22 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -1380,17 +1422,17 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
+        <a:prstDash val="dash"/>
       </a:ln>
     </cs:spPr>
   </cs:dropLine>
@@ -1399,14 +1441,14 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -1418,26 +1460,20 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
   </cs:floor>
   <cs:gridlineMajor>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
+          <a:schemeClr val="tx2">
             <a:lumMod val="15000"/>
             <a:lumOff val="85000"/>
           </a:schemeClr>
@@ -1451,96 +1487,99 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
       </a:ln>
     </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:seriesAxis>
   <cs:seriesLine>
@@ -1548,17 +1587,17 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
+        <a:prstDash val="dash"/>
       </a:ln>
     </cs:spPr>
   </cs:seriesLine>
@@ -1567,12 +1606,9 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200"/>
   </cs:title>
   <cs:trendline>
     <cs:lnRef idx="0">
@@ -1581,14 +1617,14 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="19050" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:prstDash val="sysDot"/>
+        <a:prstDash val="sysDash"/>
       </a:ln>
     </cs:spPr>
   </cs:trendline>
@@ -1597,10 +1633,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:trendlineLabel>
@@ -1609,20 +1642,19 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -1631,10 +1663,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:valueAxis>
@@ -1643,14 +1672,8 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
   </cs:wall>
 </cs:chartStyle>
 </file>
@@ -1694,6 +1717,10 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2017,7 +2044,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.5546875" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" customWidth="1"/>
     <col min="3" max="3" width="16.44140625" style="1" customWidth="1"/>
     <col min="5" max="5" width="10.77734375" customWidth="1"/>
   </cols>
@@ -2072,14 +2099,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B07C504-8045-49F4-8D07-44F7B18E5776}">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="13.6640625" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="1" max="1" width="13.6640625" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="4" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2089,11 +2117,11 @@
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E1" t="s">
+      <c r="D1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -2103,11 +2131,11 @@
       <c r="C2" s="1">
         <v>3143787.73</v>
       </c>
-      <c r="E2">
+      <c r="D2">
         <v>4352</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2117,12 +2145,11 @@
       <c r="C3" s="1">
         <v>810270.94</v>
       </c>
-      <c r="E3">
+      <c r="D3">
         <v>1235</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B4" s="2"/>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C4" s="1"/>
     </row>
   </sheetData>
